--- a/bpc_upload_template/BPC1_Upload_Template_NEW_With_Subtotals.xlsx
+++ b/bpc_upload_template/BPC1_Upload_Template_NEW_With_Subtotals.xlsx
@@ -633,7 +633,7 @@
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>2.</t>
@@ -705,7 +705,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
+    <row r="10" ht="58" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>7.</t>
